--- a/Master_Sheet.xlsx
+++ b/Master_Sheet.xlsx
@@ -795,7 +795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" style="31" min="1" max="1"/>
@@ -864,6 +864,14 @@
       <c r="A10" s="0" t="inlineStr">
         <is>
           <t>Existing staff keep their access code; new rows get a new one (see staff_codes.csv).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Staff roles: admin = Lead (dashboard + all stations), joker = all stations + dashboard, reg = Arrival/Kit/Lunch, kit = Packages (Kit/Lunch), bus = bus lead (Bus column = bus number, Point = Ramsis/October).</t>
         </is>
       </c>
     </row>
@@ -878,7 +886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" style="31" min="1" max="1"/>
@@ -928,454 +936,464 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B2" s="34" t="inlineStr">
+        <is>
+          <t>Abdelrahman Wael</t>
+        </is>
+      </c>
+      <c r="C2" s="34" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D2" s="34" t="inlineStr"/>
+      <c r="E2" s="34" t="inlineStr"/>
+      <c r="F2" s="34" t="inlineStr"/>
+      <c r="G2" s="34" t="inlineStr">
+        <is>
+          <t>01010331884</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>L2</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>Magdy</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="inlineStr"/>
+      <c r="E3" s="34" t="inlineStr"/>
+      <c r="F3" s="34" t="inlineStr"/>
+      <c r="G3" s="34" t="inlineStr">
+        <is>
+          <t>01024934700</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="34" t="inlineStr">
+        <is>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="B4" s="34" t="inlineStr">
+        <is>
+          <t>Malk Ahmed</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>joker</t>
+        </is>
+      </c>
+      <c r="D4" s="34" t="inlineStr"/>
+      <c r="E4" s="34" t="inlineStr"/>
+      <c r="F4" s="34" t="inlineStr"/>
+      <c r="G4" s="34" t="inlineStr">
+        <is>
+          <t>01090440091</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="B5" s="34" t="inlineStr">
+        <is>
+          <t>Shams Mohamd</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>joker</t>
+        </is>
+      </c>
+      <c r="D5" s="34" t="inlineStr"/>
+      <c r="E5" s="34" t="inlineStr"/>
+      <c r="F5" s="34" t="inlineStr"/>
+      <c r="G5" s="34" t="inlineStr">
+        <is>
+          <t>01015526513</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="B6" s="34" t="inlineStr">
+        <is>
+          <t>Mohamed Elalfy</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>joker</t>
+        </is>
+      </c>
+      <c r="D6" s="34" t="inlineStr"/>
+      <c r="E6" s="34" t="inlineStr"/>
+      <c r="F6" s="34" t="inlineStr"/>
+      <c r="G6" s="34" t="inlineStr">
+        <is>
+          <t>01097985342</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="34" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
-        <is>
-          <t>Coordinator Bus R1</t>
-        </is>
-      </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>Nour Ehab</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>reg</t>
+        </is>
+      </c>
+      <c r="D7" s="34" t="inlineStr"/>
+      <c r="E7" s="34" t="inlineStr"/>
+      <c r="F7" s="34" t="inlineStr"/>
+      <c r="G7" s="34" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="34" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B8" s="34" t="inlineStr">
+        <is>
+          <t>Baher Mohamed</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>reg</t>
+        </is>
+      </c>
+      <c r="D8" s="34" t="inlineStr"/>
+      <c r="E8" s="34" t="inlineStr"/>
+      <c r="F8" s="34" t="inlineStr"/>
+      <c r="G8" s="34" t="inlineStr">
+        <is>
+          <t>01040279666</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="34" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B9" s="34" t="inlineStr">
+        <is>
+          <t>Ahmed Galal</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>kit</t>
+        </is>
+      </c>
+      <c r="D9" s="34" t="inlineStr"/>
+      <c r="E9" s="34" t="inlineStr"/>
+      <c r="F9" s="34" t="inlineStr"/>
+      <c r="G9" s="34" t="inlineStr">
+        <is>
+          <t>01028065715</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>Mahmoud Farouk</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="34" t="inlineStr">
         <is>
           <t>Ramsis</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr"/>
-      <c r="G2" s="0" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B3" s="0" t="inlineStr">
-        <is>
-          <t>Coordinator Bus R2</t>
-        </is>
-      </c>
-      <c r="C3" s="0" t="inlineStr">
+      <c r="F10" s="34" t="inlineStr"/>
+      <c r="G10" s="34" t="inlineStr">
+        <is>
+          <t>01277712861</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="34" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B11" s="34" t="inlineStr">
+        <is>
+          <t>Islam Helal</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E11" s="34" t="inlineStr">
         <is>
           <t>Ramsis</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr"/>
-      <c r="G3" s="0" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="B4" s="0" t="inlineStr">
-        <is>
-          <t>Coordinator Bus R3</t>
-        </is>
-      </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="F11" s="34" t="inlineStr"/>
+      <c r="G11" s="34" t="inlineStr">
+        <is>
+          <t>01111451092</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B12" s="34" t="inlineStr">
+        <is>
+          <t>Amr Nabih</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
       </c>
-      <c r="D4" s="0" t="inlineStr">
-        <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>Ramsis</t>
         </is>
       </c>
-      <c r="F4" s="0" t="inlineStr"/>
-      <c r="G4" s="0" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="B5" s="0" t="inlineStr">
-        <is>
-          <t>Coordinator Bus R4</t>
-        </is>
-      </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr"/>
+      <c r="G12" s="34" t="inlineStr">
+        <is>
+          <t>01212551698</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="34" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B13" s="34" t="inlineStr">
+        <is>
+          <t>Mostafa Hashem</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
       </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>Ramsis</t>
         </is>
       </c>
-      <c r="F5" s="0" t="inlineStr"/>
-      <c r="G5" s="0" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="B6" s="0" t="inlineStr">
-        <is>
-          <t>Coordinator Bus R5</t>
-        </is>
-      </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="F13" s="34" t="inlineStr"/>
+      <c r="G13" s="34" t="inlineStr">
+        <is>
+          <t>01200561649</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="34" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="B14" s="34" t="inlineStr">
+        <is>
+          <t>Tarek Elsayed</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
       </c>
-      <c r="D6" s="0" t="inlineStr">
-        <is>
-          <t>R5</t>
-        </is>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="D14" s="34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E14" s="34" t="inlineStr">
         <is>
           <t>Ramsis</t>
         </is>
       </c>
-      <c r="F6" s="0" t="inlineStr"/>
-      <c r="G6" s="0" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="B7" s="0" t="inlineStr">
-        <is>
-          <t>Coordinator Bus R6</t>
-        </is>
-      </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="F14" s="34" t="inlineStr"/>
+      <c r="G14" s="34" t="inlineStr">
+        <is>
+          <t>01271311109</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B15" s="34" t="inlineStr">
+        <is>
+          <t>Omar Khaled</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
       </c>
-      <c r="D7" s="0" t="inlineStr">
-        <is>
-          <t>R6</t>
-        </is>
-      </c>
-      <c r="E7" s="0" t="inlineStr">
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E15" s="34" t="inlineStr">
         <is>
           <t>Ramsis</t>
         </is>
       </c>
-      <c r="F7" s="0" t="inlineStr"/>
-      <c r="G7" s="0" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>Coordinator Bus R7</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="F15" s="34" t="inlineStr"/>
+      <c r="G15" s="34" t="inlineStr">
+        <is>
+          <t>01005106160</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="34" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="B16" s="34" t="inlineStr">
+        <is>
+          <t>Ahmed Aboualrous</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
       </c>
-      <c r="D8" s="0" t="inlineStr">
-        <is>
-          <t>R7</t>
-        </is>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
+      <c r="D16" s="34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="34" t="inlineStr">
         <is>
           <t>Ramsis</t>
         </is>
       </c>
-      <c r="F8" s="0" t="inlineStr"/>
-      <c r="G8" s="0" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>Coordinator Bus R8</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
+      <c r="F16" s="34" t="inlineStr"/>
+      <c r="G16" s="34" t="inlineStr">
+        <is>
+          <t>01555378213</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="B17" s="34" t="inlineStr">
+        <is>
+          <t>Youmna Elhosiny</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
         <is>
           <t>bus</t>
         </is>
       </c>
-      <c r="D9" s="0" t="inlineStr">
-        <is>
-          <t>R8</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>Ramsis</t>
-        </is>
-      </c>
-      <c r="F9" s="0" t="inlineStr"/>
-      <c r="G9" s="0" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="B10" s="0" t="inlineStr">
-        <is>
-          <t>Coordinator Bus O1</t>
-        </is>
-      </c>
-      <c r="C10" s="0" t="inlineStr">
-        <is>
-          <t>bus</t>
-        </is>
-      </c>
-      <c r="D10" s="0" t="inlineStr">
-        <is>
-          <t>O1</t>
-        </is>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
+      <c r="D17" s="34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E17" s="34" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="F10" s="0" t="inlineStr"/>
-      <c r="G10" s="0" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="inlineStr">
-        <is>
-          <t>G1</t>
-        </is>
-      </c>
-      <c r="B11" s="0" t="inlineStr">
-        <is>
-          <t>Gate staff 1</t>
-        </is>
-      </c>
-      <c r="C11" s="0" t="inlineStr">
-        <is>
-          <t>gate</t>
-        </is>
-      </c>
-      <c r="D11" s="0" t="inlineStr"/>
-      <c r="E11" s="0" t="inlineStr"/>
-      <c r="F11" s="0" t="inlineStr"/>
-      <c r="G11" s="0" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="inlineStr">
-        <is>
-          <t>G2</t>
-        </is>
-      </c>
-      <c r="B12" s="0" t="inlineStr">
-        <is>
-          <t>Gate staff 2</t>
-        </is>
-      </c>
-      <c r="C12" s="0" t="inlineStr">
-        <is>
-          <t>gate</t>
-        </is>
-      </c>
-      <c r="D12" s="0" t="inlineStr"/>
-      <c r="E12" s="0" t="inlineStr"/>
-      <c r="F12" s="0" t="inlineStr"/>
-      <c r="G12" s="0" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="inlineStr">
-        <is>
-          <t>K1</t>
-        </is>
-      </c>
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>Kit desk 1</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>kit</t>
-        </is>
-      </c>
-      <c r="D13" s="0" t="inlineStr"/>
-      <c r="E13" s="0" t="inlineStr"/>
-      <c r="F13" s="0" t="inlineStr"/>
-      <c r="G13" s="0" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="inlineStr">
-        <is>
-          <t>L1</t>
-        </is>
-      </c>
-      <c r="B14" s="0" t="inlineStr">
-        <is>
-          <t>Lunch desk 1</t>
-        </is>
-      </c>
-      <c r="C14" s="0" t="inlineStr">
-        <is>
-          <t>lunch</t>
-        </is>
-      </c>
-      <c r="D14" s="0" t="inlineStr"/>
-      <c r="E14" s="0" t="inlineStr"/>
-      <c r="F14" s="0" t="inlineStr"/>
-      <c r="G14" s="0" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="inlineStr">
-        <is>
-          <t>ACT1</t>
-        </is>
-      </c>
-      <c r="B15" s="0" t="inlineStr">
-        <is>
-          <t>Activity 1 staff</t>
-        </is>
-      </c>
-      <c r="C15" s="0" t="inlineStr">
-        <is>
-          <t>a1</t>
-        </is>
-      </c>
-      <c r="D15" s="0" t="inlineStr"/>
-      <c r="E15" s="0" t="inlineStr"/>
-      <c r="F15" s="0" t="inlineStr"/>
-      <c r="G15" s="0" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="inlineStr">
-        <is>
-          <t>ACT2</t>
-        </is>
-      </c>
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t>Activity 2 staff</t>
-        </is>
-      </c>
-      <c r="C16" s="0" t="inlineStr">
-        <is>
-          <t>a2</t>
-        </is>
-      </c>
-      <c r="D16" s="0" t="inlineStr"/>
-      <c r="E16" s="0" t="inlineStr"/>
-      <c r="F16" s="0" t="inlineStr"/>
-      <c r="G16" s="0" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="inlineStr">
-        <is>
-          <t>ACT3</t>
-        </is>
-      </c>
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t>Activity 3 staff</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="inlineStr">
-        <is>
-          <t>a3</t>
-        </is>
-      </c>
-      <c r="D17" s="0" t="inlineStr"/>
-      <c r="E17" s="0" t="inlineStr"/>
-      <c r="F17" s="0" t="inlineStr"/>
-      <c r="G17" s="0" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="inlineStr">
-        <is>
-          <t>TB1</t>
-        </is>
-      </c>
-      <c r="B18" s="0" t="inlineStr">
-        <is>
-          <t>Transport back staff</t>
-        </is>
-      </c>
-      <c r="C18" s="0" t="inlineStr">
-        <is>
-          <t>back</t>
-        </is>
-      </c>
-      <c r="D18" s="0" t="inlineStr"/>
-      <c r="E18" s="0" t="inlineStr"/>
-      <c r="F18" s="0" t="inlineStr"/>
-      <c r="G18" s="0" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="inlineStr">
-        <is>
-          <t>ADMIN</t>
-        </is>
-      </c>
-      <c r="B19" s="0" t="inlineStr">
-        <is>
-          <t>Admin</t>
-        </is>
-      </c>
-      <c r="C19" s="0" t="inlineStr">
-        <is>
-          <t>admin</t>
-        </is>
-      </c>
-      <c r="D19" s="0" t="inlineStr"/>
-      <c r="E19" s="0" t="inlineStr"/>
-      <c r="F19" s="0" t="inlineStr"/>
-      <c r="G19" s="0" t="inlineStr"/>
+      <c r="F17" s="34" t="inlineStr"/>
+      <c r="G17" s="34" t="inlineStr">
+        <is>
+          <t>01555155530</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1499,7 +1517,7 @@
           <t>28608250202036</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -1548,7 +1566,7 @@
           <t>28407152303813</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -1597,7 +1615,7 @@
           <t>28607152301925</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -1646,7 +1664,7 @@
           <t>31505292301963</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1695,7 +1713,7 @@
           <t>30904262300677</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -1744,7 +1762,7 @@
           <t>31107152301437</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -1793,7 +1811,7 @@
           <t>32010302300566</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -1842,7 +1860,7 @@
           <t>27708201401059</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -1891,7 +1909,7 @@
           <t>27603151302872</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -1940,7 +1958,7 @@
           <t>29105122300094</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -1989,7 +2007,7 @@
           <t>27510288800057</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -2038,7 +2056,7 @@
           <t>28511190101169</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -2087,7 +2105,7 @@
           <t>27605050200907</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -4656,7 +4674,7 @@
           <t>30210010123762</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -4705,7 +4723,7 @@
           <t>30409161702552</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -4754,7 +4772,7 @@
           <t>29901051402711</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -4803,7 +4821,7 @@
           <t>30111110102764</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -4852,7 +4870,7 @@
           <t>30304011406959</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -4901,7 +4919,7 @@
           <t>29807251403635</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -4950,7 +4968,7 @@
           <t>30607071401061</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -4999,7 +5017,7 @@
           <t>30402081702573</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -5048,7 +5066,7 @@
           <t>30304140100939</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -5097,7 +5115,7 @@
           <t>30311090103997</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -5146,7 +5164,7 @@
           <t>30302140201317</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -5195,7 +5213,7 @@
           <t>30408110103747</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5244,7 +5262,7 @@
           <t>30512182102925</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5293,7 +5311,7 @@
           <t>30602191602204</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -5342,7 +5360,7 @@
           <t>30302171200653</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -5391,7 +5409,7 @@
           <t>30312200203557</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -5440,7 +5458,7 @@
           <t>30403160100836</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -5489,7 +5507,7 @@
           <t>306009070101989</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -5538,7 +5556,7 @@
           <t>30802028800626</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5587,7 +5605,7 @@
           <t>30209151702733</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J21" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -5636,7 +5654,7 @@
           <t>30710300100181</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J22" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5685,7 +5703,7 @@
           <t>30710300100181</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J23" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -5734,7 +5752,7 @@
           <t>30708270103291</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J24" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -5783,7 +5801,7 @@
           <t>30708270103291</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J25" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -5832,7 +5850,7 @@
           <t>30502071400255</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J26" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -5881,7 +5899,7 @@
           <t>30305062101571</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J27" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -5930,7 +5948,7 @@
           <t>30007060102804</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J28" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -5979,7 +5997,7 @@
           <t>30208203100064</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J29" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -6028,7 +6046,7 @@
           <t>30207130101621</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J30" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -6077,7 +6095,7 @@
           <t>30208131702161</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J31" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -6126,7 +6144,7 @@
           <t>30203052100529</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J32" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -6175,7 +6193,7 @@
           <t>29810221300948</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J33" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -6224,7 +6242,7 @@
           <t>30311090103997</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="J34" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -6273,7 +6291,7 @@
           <t>30010192300703</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="J35" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -6322,7 +6340,7 @@
           <t>30103200201424</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="J36" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -6371,7 +6389,7 @@
           <t>30210010109085</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="J37" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -6420,7 +6438,7 @@
           <t>.</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="J38" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -8869,7 +8887,7 @@
           <t>30405091400167</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -8918,7 +8936,7 @@
           <t>30205290102168</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -8967,7 +8985,7 @@
           <t>309080714401088</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -9016,7 +9034,7 @@
           <t>30002021807424</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -9065,7 +9083,7 @@
           <t>30703231400333</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -9114,7 +9132,7 @@
           <t>28407271301179</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -9163,7 +9181,7 @@
           <t>30207151203599</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -11772,7 +11790,7 @@
           <t>29707021400098</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -11821,7 +11839,7 @@
           <t>30409301500165</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -11870,7 +11888,7 @@
           <t>29707221400092</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -11919,7 +11937,7 @@
           <t>30212022300301</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -11968,7 +11986,7 @@
           <t>30202052303229</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -12017,7 +12035,7 @@
           <t>30210171900513</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -12066,7 +12084,7 @@
           <t>30402262102578</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -12115,7 +12133,7 @@
           <t>30310012716501</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -12164,7 +12182,7 @@
           <t>30501011206291</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -12213,7 +12231,7 @@
           <t>3001223150114</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -12262,7 +12280,7 @@
           <t>30204011813673</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -12311,7 +12329,7 @@
           <t>30101011293552</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -12360,7 +12378,7 @@
           <t>30508270200212</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -12409,7 +12427,7 @@
           <t>30602030200572</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -12458,7 +12476,7 @@
           <t>30208080203173</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -12507,7 +12525,7 @@
           <t>30105278801056</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -12556,7 +12574,7 @@
           <t>30409091206692</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -12605,7 +12623,7 @@
           <t>30306091701649</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -12654,7 +12672,7 @@
           <t>30401278800708</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J20" s="0" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -15195,7 +15213,7 @@
           <t>30403031302066</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -15246,7 +15264,7 @@
           <t>30412218800727</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -15297,7 +15315,7 @@
           <t>30507191600209</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -15348,7 +15366,7 @@
           <t>30703122200855</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -15399,7 +15417,7 @@
           <t>30410041700236</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -15450,7 +15468,7 @@
           <t>30607070100084</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -15501,7 +15519,7 @@
           <t>30707071306543</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -15552,7 +15570,7 @@
           <t>30407150104812</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -15603,7 +15621,7 @@
           <t>30503031201353</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -15654,7 +15672,7 @@
           <t>30405241500661</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -15705,7 +15723,7 @@
           <t>30404012108557</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -15756,7 +15774,7 @@
           <t>30610031401264</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -15807,7 +15825,7 @@
           <t>30609291404803</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -15858,7 +15876,7 @@
           <t>30707222201668</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -15909,7 +15927,7 @@
           <t>30510010124479</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -15960,7 +15978,7 @@
           <t>30411090201594</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -18525,7 +18543,7 @@
           <t>30406162500156</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -18579,7 +18597,7 @@
           <t>30403211301165</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -18633,7 +18651,7 @@
           <t>30507011315161</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -18687,7 +18705,7 @@
           <t>3030929100944</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -18741,7 +18759,7 @@
           <t>30405091501303</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -18795,7 +18813,7 @@
           <t>30202012504132</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -18849,7 +18867,7 @@
           <t>30212212700055</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K8" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -18903,7 +18921,7 @@
           <t>30310031100384</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K9" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -18957,7 +18975,7 @@
           <t>30308010109328</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -19011,7 +19029,7 @@
           <t>30510011211596</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="K11" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -19065,7 +19083,7 @@
           <t>30209291205683</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -19119,7 +19137,7 @@
           <t>30603180201263</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="K13" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -19173,7 +19191,7 @@
           <t>30705020201876</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="K14" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -19227,7 +19245,7 @@
           <t>30605111801324</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="K15" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -19281,7 +19299,7 @@
           <t>30410158800479</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="K16" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -19335,7 +19353,7 @@
           <t>30504011100247</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K17" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -19389,7 +19407,7 @@
           <t>00000000</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K18" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -19443,7 +19461,7 @@
           <t>00000000</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K19" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -19497,7 +19515,7 @@
           <t>00000000</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="K20" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -19551,7 +19569,7 @@
           <t>30411172105399</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -19605,7 +19623,7 @@
           <t>30506272102436</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="K22" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -19659,7 +19677,7 @@
           <t>30402018800158</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="K23" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -19713,7 +19731,7 @@
           <t>30207248800273</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="K24" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -19767,7 +19785,7 @@
           <t>30511161302855</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="K25" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -19821,7 +19839,7 @@
           <t>30408248801194</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K26" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -19875,7 +19893,7 @@
           <t>30404012603477</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K27" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -19929,7 +19947,7 @@
           <t>30409061400532</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -19983,7 +20001,7 @@
           <t>30207161402573</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -20037,7 +20055,7 @@
           <t>30606201400198</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -20091,7 +20109,7 @@
           <t>30503211402195</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -20145,7 +20163,7 @@
           <t>30902020600088</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="K32" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -20199,7 +20217,7 @@
           <t>30602061400596</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="K33" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -20253,7 +20271,7 @@
           <t>30409061400532</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="K34" s="0" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -20307,7 +20325,7 @@
           <t>30406182600165</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="K35" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -20361,7 +20379,7 @@
           <t>30505051404571</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K36" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -20415,7 +20433,7 @@
           <t>30608201402142</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="K37" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -20469,7 +20487,7 @@
           <t>30603141403258</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="K38" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -20523,7 +20541,7 @@
           <t>30603211400537</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="K39" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -20577,7 +20595,7 @@
           <t>30408210101938</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="K40" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -20631,7 +20649,7 @@
           <t>30505271401557</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="K41" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -20685,7 +20703,7 @@
           <t>30504301400732</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="K42" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -20739,7 +20757,7 @@
           <t>30508221710214</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K43" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -20793,7 +20811,7 @@
           <t>30601191401113</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="K44" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -20847,7 +20865,7 @@
           <t>30509101401116</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K45" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -20901,7 +20919,7 @@
           <t>30412041402831</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K46" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -20955,7 +20973,7 @@
           <t>30412062200058</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="K47" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -21009,7 +21027,7 @@
           <t>30611062202207</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="K48" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -21063,7 +21081,7 @@
           <t>30506122200324</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="K49" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -21117,7 +21135,7 @@
           <t>30712012202096</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="K50" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -21171,7 +21189,7 @@
           <t>30406172501053</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="K51" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -21225,7 +21243,7 @@
           <t>30608062401888</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K52" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -21279,7 +21297,7 @@
           <t>30604038800609</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="K53" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -21333,7 +21351,7 @@
           <t>30402172701006</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="K54" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -21387,7 +21405,7 @@
           <t>30604042200805</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="K55" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -21441,7 +21459,7 @@
           <t>30305122301443</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="K56" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -21495,7 +21513,7 @@
           <t>30408302103007</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="K57" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -21549,7 +21567,7 @@
           <t>30601012204505</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="K58" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -21603,7 +21621,7 @@
           <t>30201181601256</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="K59" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -21657,7 +21675,7 @@
           <t>30401182201072</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K60" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -21711,7 +21729,7 @@
           <t>30402172700964</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K61" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -21765,7 +21783,7 @@
           <t>30402230102975</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="K62" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -21819,7 +21837,7 @@
           <t>30511030101838</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K63" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -21873,7 +21891,7 @@
           <t>30409061402357</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="K64" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -21927,7 +21945,7 @@
           <t>30509020104575</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="K65" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -21981,7 +21999,7 @@
           <t>30305272100551</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="K66" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -22035,7 +22053,7 @@
           <t>30308121202653</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="K67" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -22089,7 +22107,7 @@
           <t>30611051203155</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="K68" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -22143,7 +22161,7 @@
           <t>30502141202995</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="K69" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -22197,7 +22215,7 @@
           <t>30712201204105</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="K70" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -22251,7 +22269,7 @@
           <t>30405238800395</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K71" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -22305,7 +22323,7 @@
           <t>30702011102319</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="K72" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -22359,7 +22377,7 @@
           <t>30506281801959</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="K73" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -22413,7 +22431,7 @@
           <t>30506021300417</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="K74" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -22467,7 +22485,7 @@
           <t>30412090105834</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K75" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -22521,7 +22539,7 @@
           <t>30610318800623</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="K76" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -22575,7 +22593,7 @@
           <t>30607230100205</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="K77" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -22629,7 +22647,7 @@
           <t>30504192602338</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="K78" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -22683,7 +22701,7 @@
           <t>30406270101535</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="K79" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -22737,7 +22755,7 @@
           <t>30508180100812</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="K80" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -22791,7 +22809,7 @@
           <t>30601180101096</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="K81" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -22845,7 +22863,7 @@
           <t>30412221701616</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="K82" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -22899,7 +22917,7 @@
           <t>30505110104544</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K83" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -22953,7 +22971,7 @@
           <t>30412121701074</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="K84" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -23007,7 +23025,7 @@
           <t>30401100107227</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="K85" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -23061,7 +23079,7 @@
           <t>30610160200127</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="K86" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -23115,7 +23133,7 @@
           <t>30501070104141</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K87" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -23169,7 +23187,7 @@
           <t>30408122200071</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K88" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -23223,7 +23241,7 @@
           <t>30407240202228</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K89" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -23277,7 +23295,7 @@
           <t>30307210202598</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="K90" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -23331,7 +23349,7 @@
           <t>30310111700498</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="K91" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -23385,7 +23403,7 @@
           <t>30401278800724</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="K92" s="0" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -23439,7 +23457,7 @@
           <t>30410121402201</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="K93" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -23493,7 +23511,7 @@
           <t>30602011402709</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="K94" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -23547,7 +23565,7 @@
           <t>30511040202012</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="K95" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -23601,7 +23619,7 @@
           <t>30508081202069</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="K96" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -23655,7 +23673,7 @@
           <t>30504013301045</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="K97" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -23709,7 +23727,7 @@
           <t>30610231800961</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="K98" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -23763,7 +23781,7 @@
           <t>30406010105464</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="K99" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -23817,7 +23835,7 @@
           <t>30612070100339</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="K100" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -23871,7 +23889,7 @@
           <t>30705010112212</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="K101" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -23925,7 +23943,7 @@
           <t>30605260102587</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K102" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -23979,7 +23997,7 @@
           <t>30603160103923</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K103" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -24033,7 +24051,7 @@
           <t>30511170107178</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K104" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -24087,7 +24105,7 @@
           <t>30701150100219</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K105" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -24141,7 +24159,7 @@
           <t>30407180106313</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="K106" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -24195,7 +24213,7 @@
           <t>30405011804637</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="K107" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -24249,7 +24267,7 @@
           <t>30709248800449</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="K108" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -24303,7 +24321,7 @@
           <t>30707071212476</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="K109" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -24357,7 +24375,7 @@
           <t>30702071301752</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K110" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -24411,7 +24429,7 @@
           <t>30604050105099</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="K111" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -24465,7 +24483,7 @@
           <t>30601040104516</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="K112" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -24519,7 +24537,7 @@
           <t>30704290102946</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="K113" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -24573,7 +24591,7 @@
           <t>30408132101918</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="K114" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -24627,7 +24645,7 @@
           <t>30411070201512</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="K115" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -24681,7 +24699,7 @@
           <t>30509092103379</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="K116" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -24735,7 +24753,7 @@
           <t>30510231200102</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="K117" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -24789,7 +24807,7 @@
           <t>30501300101392</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="K118" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -24843,7 +24861,7 @@
           <t>30712011603461</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="K119" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -24897,7 +24915,7 @@
           <t>30406171600228</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="K120" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -24951,7 +24969,7 @@
           <t>30410280200334</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="K121" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -25005,7 +25023,7 @@
           <t>30506051301515</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="K122" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -25059,7 +25077,7 @@
           <t>30702012502469</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="K123" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -25113,7 +25131,7 @@
           <t>30407050100135</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="K124" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -25167,7 +25185,7 @@
           <t>30803060104581</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="K125" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -25221,7 +25239,7 @@
           <t>30609210106528</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="K126" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -25275,7 +25293,7 @@
           <t>30601311401007</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
+      <c r="K127" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -25329,7 +25347,7 @@
           <t>30603300103112</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr">
+      <c r="K128" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -25383,7 +25401,7 @@
           <t>30501012300437</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr">
+      <c r="K129" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -25437,7 +25455,7 @@
           <t>30611012306079</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="K130" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -25491,7 +25509,7 @@
           <t>30608102303256</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr">
+      <c r="K131" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -25545,7 +25563,7 @@
           <t>30609302303516</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr">
+      <c r="K132" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -25599,7 +25617,7 @@
           <t>30708272301422</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr">
+      <c r="K133" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -25653,7 +25671,7 @@
           <t>30603232302055</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="K134" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -25707,7 +25725,7 @@
           <t>30511072301918</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr">
+      <c r="K135" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -25761,7 +25779,7 @@
           <t>30508171500158</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr">
+      <c r="K136" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -25815,7 +25833,7 @@
           <t>30505050104159</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr">
+      <c r="K137" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -25869,7 +25887,7 @@
           <t>30311082300031</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="K138" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -25923,7 +25941,7 @@
           <t>30706010202544</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr">
+      <c r="K139" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -25977,7 +25995,7 @@
           <t>30601232300335</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr">
+      <c r="K140" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -26031,7 +26049,7 @@
           <t>60407042300214</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr">
+      <c r="K141" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -26085,7 +26103,7 @@
           <t>30701122301624</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr">
+      <c r="K142" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -26139,7 +26157,7 @@
           <t>30208108800423</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="K143" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -26193,7 +26211,7 @@
           <t>30701012310415</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="K144" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -26247,7 +26265,7 @@
           <t>30709122302427</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr">
+      <c r="K145" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -26301,7 +26319,7 @@
           <t>30707260104501</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr">
+      <c r="K146" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -26355,7 +26373,7 @@
           <t>30712231401274</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
+      <c r="K147" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -26409,7 +26427,7 @@
           <t>30701062102694</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr">
+      <c r="K148" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -26463,7 +26481,7 @@
           <t>30201011637957</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="K149" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -26517,7 +26535,7 @@
           <t>30105020200694</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="K150" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -26571,7 +26589,7 @@
           <t>30603200103948</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
+      <c r="K151" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -26625,7 +26643,7 @@
           <t>30608201309754</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr">
+      <c r="K152" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -26679,7 +26697,7 @@
           <t>30612020200065</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr">
+      <c r="K153" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -26733,7 +26751,7 @@
           <t>30704050400117</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr">
+      <c r="K154" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -26787,7 +26805,7 @@
           <t>30706162402166</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="K155" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -26841,7 +26859,7 @@
           <t>30707010401195</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr">
+      <c r="K156" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -26895,7 +26913,7 @@
           <t>30206101702598</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr">
+      <c r="K157" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -26949,7 +26967,7 @@
           <t>30303271400796</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr">
+      <c r="K158" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -27003,7 +27021,7 @@
           <t>30611100104214</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
+      <c r="K159" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -27057,7 +27075,7 @@
           <t>30605272103554</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="K160" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -27111,7 +27129,7 @@
           <t>30606290102227</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr">
+      <c r="K161" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -27165,7 +27183,7 @@
           <t>30602090107237</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="K162" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -27219,7 +27237,7 @@
           <t>30409111400628</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
+      <c r="K163" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -27273,7 +27291,7 @@
           <t>302011223008</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr">
+      <c r="K164" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -27327,7 +27345,7 @@
           <t>30707040101552</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr">
+      <c r="K165" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -27381,7 +27399,7 @@
           <t>30504220100254</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="K166" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -27435,7 +27453,7 @@
           <t>30512170101192</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr">
+      <c r="K167" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -27489,7 +27507,7 @@
           <t>30505082301703</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr">
+      <c r="K168" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -27543,7 +27561,7 @@
           <t>30506261301518</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr">
+      <c r="K169" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -27597,7 +27615,7 @@
           <t>30509263100212</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr">
+      <c r="K170" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -27651,7 +27669,7 @@
           <t>30609288801338</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr">
+      <c r="K171" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -27705,7 +27723,7 @@
           <t>30308288800072</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr">
+      <c r="K172" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -27759,7 +27777,7 @@
           <t>30103151101389</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
+      <c r="K173" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -27813,7 +27831,7 @@
           <t>30406161101193</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr">
+      <c r="K174" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -27867,7 +27885,7 @@
           <t>30405011302178</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr">
+      <c r="K175" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -27921,7 +27939,7 @@
           <t>30510123300133</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr">
+      <c r="K176" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -27975,7 +27993,7 @@
           <t>30307088801094</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr">
+      <c r="K177" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -28029,7 +28047,7 @@
           <t>30502201204372</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="K178" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -28083,7 +28101,7 @@
           <t>30505041100132</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr">
+      <c r="K179" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -28137,7 +28155,7 @@
           <t>30403101100415</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="K180" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -28191,7 +28209,7 @@
           <t>30503091100734</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr">
+      <c r="K181" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -28245,7 +28263,7 @@
           <t>30402201100076</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="K182" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -28299,7 +28317,7 @@
           <t>30312011308755</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr">
+      <c r="K183" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -28353,7 +28371,7 @@
           <t>30507102701757</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
+      <c r="K184" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -28407,7 +28425,7 @@
           <t>30603271100427</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="K185" s="0" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -28461,7 +28479,7 @@
           <t>30501231200758</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr">
+      <c r="K186" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -28515,7 +28533,7 @@
           <t>30602271100544</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
+      <c r="K187" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -28569,7 +28587,7 @@
           <t>30609261100761</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr">
+      <c r="K188" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -28623,7 +28641,7 @@
           <t>30411211202291</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr">
+      <c r="K189" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -28677,7 +28695,7 @@
           <t>30408101100123</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr">
+      <c r="K190" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -28731,7 +28749,7 @@
           <t>30405101100361</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr">
+      <c r="K191" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -28785,7 +28803,7 @@
           <t>30401111100445</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr">
+      <c r="K192" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -28839,7 +28857,7 @@
           <t>30408101100166</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="K193" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -28893,7 +28911,7 @@
           <t>30412268800132</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr">
+      <c r="K194" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -28947,7 +28965,7 @@
           <t>30707150100411</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr">
+      <c r="K195" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -29001,7 +29019,7 @@
           <t>30506041401333</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr">
+      <c r="K196" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -29055,7 +29073,7 @@
           <t>30410011819352</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr">
+      <c r="K197" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -29109,7 +29127,7 @@
           <t>30408040103728</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr">
+      <c r="K198" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -29163,7 +29181,7 @@
           <t>30503151401585</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="K199" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -29217,7 +29235,7 @@
           <t>304110706625</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr">
+      <c r="K200" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -29271,7 +29289,7 @@
           <t>304090101016</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr">
+      <c r="K201" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -29325,7 +29343,7 @@
           <t>30305012600038</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="K202" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -29379,7 +29397,7 @@
           <t>30308061602495</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="K203" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -29433,7 +29451,7 @@
           <t>30510311200685</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="K204" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -29487,7 +29505,7 @@
           <t>30602111200224</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="K205" s="0" t="inlineStr">
         <is>
           <t>S</t>
         </is>
@@ -29541,7 +29559,7 @@
           <t>30603241200435</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="K206" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -29595,7 +29613,7 @@
           <t>30605271200068</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="K207" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -29649,7 +29667,7 @@
           <t>30506161600402</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="K208" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -29703,7 +29721,7 @@
           <t>30506081200365</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="K209" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -29757,7 +29775,7 @@
           <t>30607071202557</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="K210" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -29811,7 +29829,7 @@
           <t>30509151207779</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="K211" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -29865,7 +29883,7 @@
           <t>30508271201816</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="K212" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -29919,7 +29937,7 @@
           <t>30406011207449</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="K213" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -29973,7 +29991,7 @@
           <t>30505221201328</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr">
+      <c r="K214" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -30027,7 +30045,7 @@
           <t>30701221202751</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="K215" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -30081,7 +30099,7 @@
           <t>30708141603474</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="K216" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -30135,7 +30153,7 @@
           <t>30605101201035</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="K217" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -30189,7 +30207,7 @@
           <t>30609291202992</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="K218" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -30243,7 +30261,7 @@
           <t>30701011246195</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="K219" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -30297,7 +30315,7 @@
           <t>30602258800359</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="K220" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -30351,7 +30369,7 @@
           <t>30506211200583</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="K221" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -30405,7 +30423,7 @@
           <t>30309201210718</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="K222" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -30459,7 +30477,7 @@
           <t>30602041201937</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="K223" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -30513,7 +30531,7 @@
           <t>30510011200233</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="K224" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -30567,7 +30585,7 @@
           <t>305040112123347</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="K225" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -30621,7 +30639,7 @@
           <t>30608181200149</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="K226" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -30675,7 +30693,7 @@
           <t>30601011236314</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="K227" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -30729,7 +30747,7 @@
           <t>30506141200394</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="K228" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -30783,7 +30801,7 @@
           <t>30306221703045</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
+      <c r="K229" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -30837,7 +30855,7 @@
           <t>30207161601967</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="K230" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -30891,7 +30909,7 @@
           <t>30407281700054</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr">
+      <c r="K231" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -30945,7 +30963,7 @@
           <t>30604101701619</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="K232" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -30999,7 +31017,7 @@
           <t>30512051802581</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="K233" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -31053,7 +31071,7 @@
           <t>30611041700428</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="K234" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -31107,7 +31125,7 @@
           <t>30607091700065</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="K235" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -31161,7 +31179,7 @@
           <t>30411031702318</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="K236" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -31215,7 +31233,7 @@
           <t>30409181900822</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
+      <c r="K237" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -31269,7 +31287,7 @@
           <t>01093309673</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="K238" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -31323,7 +31341,7 @@
           <t>30711308800332</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="K239" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -31377,7 +31395,7 @@
           <t>30409131701187</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="K240" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -31431,7 +31449,7 @@
           <t>30407191700195</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr">
+      <c r="K241" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -31485,7 +31503,7 @@
           <t>30212171601454</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr">
+      <c r="K242" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -31539,7 +31557,7 @@
           <t>30511191700499</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr">
+      <c r="K243" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -31593,7 +31611,7 @@
           <t>30501230101055</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr">
+      <c r="K244" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -31647,7 +31665,7 @@
           <t>30610201304137</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr">
+      <c r="K245" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -31701,7 +31719,7 @@
           <t>30408262301897</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr">
+      <c r="K246" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -31755,7 +31773,7 @@
           <t>30407052104855</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr">
+      <c r="K247" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -31809,7 +31827,7 @@
           <t>30406130103236</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr">
+      <c r="K248" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -31863,7 +31881,7 @@
           <t>30305010106451</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr">
+      <c r="K249" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -31917,7 +31935,7 @@
           <t>30403262700196</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr">
+      <c r="K250" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -31971,7 +31989,7 @@
           <t>30405052404481</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr">
+      <c r="K251" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -32025,7 +32043,7 @@
           <t>30403082102274</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr">
+      <c r="K252" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -32079,7 +32097,7 @@
           <t>30509072200084</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr">
+      <c r="K253" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -32133,7 +32151,7 @@
           <t>30601012211781</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr">
+      <c r="K254" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -32187,7 +32205,7 @@
           <t>30512012205169</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr">
+      <c r="K255" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -32241,7 +32259,7 @@
           <t>30602261300308</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr">
+      <c r="K256" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -32295,7 +32313,7 @@
           <t>30407292200517</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr">
+      <c r="K257" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -32349,7 +32367,7 @@
           <t>29003030100938</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr">
+      <c r="K258" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -32403,7 +32421,7 @@
           <t>30006162300752</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr">
+      <c r="K259" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -32457,7 +32475,7 @@
           <t>30509182300602</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="K260" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -32511,7 +32529,7 @@
           <t>30603011403841</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
+      <c r="K261" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -32565,7 +32583,7 @@
           <t>30505131701046</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
+      <c r="K262" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -32619,7 +32637,7 @@
           <t>30510291700147</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="K263" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -32673,7 +32691,7 @@
           <t>30608072301024</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="K264" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -32727,7 +32745,7 @@
           <t>30505050103683</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
+      <c r="K265" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -32781,7 +32799,7 @@
           <t>30502110102461</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="K266" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -32835,7 +32853,7 @@
           <t>30608241401017</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
+      <c r="K267" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -32889,7 +32907,7 @@
           <t>30709092102592</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr">
+      <c r="K268" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -32943,7 +32961,7 @@
           <t>30705172100056</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
+      <c r="K269" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -32997,7 +33015,7 @@
           <t>30301201301356</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr">
+      <c r="K270" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -33051,7 +33069,7 @@
           <t>30605011507763</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr">
+      <c r="K271" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -33146,7 +33164,7 @@
           <t>30604230102942</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr">
+      <c r="K273" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -33200,7 +33218,7 @@
           <t>30305211400935</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr">
+      <c r="K274" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -33254,7 +33272,7 @@
           <t>30312260103918</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr">
+      <c r="K275" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -33308,7 +33326,7 @@
           <t>30202171300076</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr">
+      <c r="K276" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -33362,7 +33380,7 @@
           <t>3012140100087</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr">
+      <c r="K277" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -33416,7 +33434,7 @@
           <t>30211260106169</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
+      <c r="K278" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -33470,7 +33488,7 @@
           <t>30404010106824</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr">
+      <c r="K279" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -33524,7 +33542,7 @@
           <t>30312110105661</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr">
+      <c r="K280" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -33578,7 +33596,7 @@
           <t>306011091301524</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr">
+      <c r="K281" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -33632,7 +33650,7 @@
           <t>30211128800714</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="K282" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -33686,7 +33704,7 @@
           <t>30504108800316</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr">
+      <c r="K283" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -33740,7 +33758,7 @@
           <t>30408150104053</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr">
+      <c r="K284" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -33794,7 +33812,7 @@
           <t>30309280109024</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr">
+      <c r="K285" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -33848,7 +33866,7 @@
           <t>30412181401185</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr">
+      <c r="K286" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -33902,7 +33920,7 @@
           <t>30408040103841</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
+      <c r="K287" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -33956,7 +33974,7 @@
           <t>30404151300616</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr">
+      <c r="K288" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -34010,7 +34028,7 @@
           <t>30401161301093</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr">
+      <c r="K289" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -34064,7 +34082,7 @@
           <t>30603240103576</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr">
+      <c r="K290" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -34118,7 +34136,7 @@
           <t>30601010102314</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr">
+      <c r="K291" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -34172,7 +34190,7 @@
           <t>30706040104512</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr">
+      <c r="K292" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -34226,7 +34244,7 @@
           <t>30611050101413</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr">
+      <c r="K293" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -34280,7 +34298,7 @@
           <t>30802040102306</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr">
+      <c r="K294" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -34334,7 +34352,7 @@
           <t>30110011306297</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr">
+      <c r="K295" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -34388,7 +34406,7 @@
           <t>30308100202734</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr">
+      <c r="K296" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -34442,7 +34460,7 @@
           <t>30606220201139</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr">
+      <c r="K297" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -34496,7 +34514,7 @@
           <t>⁠30604161501996</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr">
+      <c r="K298" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -34550,7 +34568,7 @@
           <t>30504258800055</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr">
+      <c r="K299" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -34604,7 +34622,7 @@
           <t>30611011502133</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr">
+      <c r="K300" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -34658,7 +34676,7 @@
           <t>3078110202099</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr">
+      <c r="K301" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -34712,7 +34730,7 @@
           <t>30606291802583</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr">
+      <c r="K302" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -34766,7 +34784,7 @@
           <t>30603082601644</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr">
+      <c r="K303" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -34820,7 +34838,7 @@
           <t>30604032600163</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr">
+      <c r="K304" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -34874,7 +34892,7 @@
           <t>30703142600418</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr">
+      <c r="K305" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -34928,7 +34946,7 @@
           <t>30707202604421</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr">
+      <c r="K306" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -34982,7 +35000,7 @@
           <t>30605172200722</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr">
+      <c r="K307" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -35036,7 +35054,7 @@
           <t>30712082400642</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr">
+      <c r="K308" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -35090,7 +35108,7 @@
           <t>30509222200916</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr">
+      <c r="K309" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -35144,7 +35162,7 @@
           <t>30409072300351</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr">
+      <c r="K310" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -35198,7 +35216,7 @@
           <t>30407302501464</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr">
+      <c r="K311" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -35252,7 +35270,7 @@
           <t>30503012707971</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr">
+      <c r="K312" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -35306,7 +35324,7 @@
           <t>30407132702435</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr">
+      <c r="K313" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -35360,7 +35378,7 @@
           <t>30306151401216</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr">
+      <c r="K314" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -35414,7 +35432,7 @@
           <t>30409202700101</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr">
+      <c r="K315" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -35468,7 +35486,7 @@
           <t>30504282700266</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr">
+      <c r="K316" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -35522,7 +35540,7 @@
           <t>30611112702302</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr">
+      <c r="K317" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -35576,7 +35594,7 @@
           <t>30509302701665</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr">
+      <c r="K318" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -35630,7 +35648,7 @@
           <t>30506041700519</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
+      <c r="K319" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -35684,7 +35702,7 @@
           <t>30504041900353</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr">
+      <c r="K320" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -35738,7 +35756,7 @@
           <t>30611301900175</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr">
+      <c r="K321" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -35792,7 +35810,7 @@
           <t>30310211200352</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr">
+      <c r="K322" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -35846,7 +35864,7 @@
           <t>30501128800259</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr">
+      <c r="K323" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -35900,7 +35918,7 @@
           <t>30404261200773</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr">
+      <c r="K324" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -35954,7 +35972,7 @@
           <t>30411011900415</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr">
+      <c r="K325" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -36008,7 +36026,7 @@
           <t>30512308800992</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr">
+      <c r="K326" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -36062,7 +36080,7 @@
           <t>30301098800136</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr">
+      <c r="K327" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -36116,7 +36134,7 @@
           <t>30310011208537</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr">
+      <c r="K328" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -36170,7 +36188,7 @@
           <t>30312041900195</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr">
+      <c r="K329" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -36224,7 +36242,7 @@
           <t>⁠30407281700097</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr">
+      <c r="K330" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -36278,7 +36296,7 @@
           <t>30411221302677</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr">
+      <c r="K331" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -36332,7 +36350,7 @@
           <t>30308271301137</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr">
+      <c r="K332" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -36386,7 +36404,7 @@
           <t>30405181302253</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr">
+      <c r="K333" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -36440,7 +36458,7 @@
           <t>30403171302856</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr">
+      <c r="K334" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -36494,7 +36512,7 @@
           <t>30405021303555</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr">
+      <c r="K335" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -36548,7 +36566,7 @@
           <t>30611071301552</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr">
+      <c r="K336" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -36602,7 +36620,7 @@
           <t>30305081302235</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr">
+      <c r="K337" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -36656,7 +36674,7 @@
           <t>30410190201145</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr">
+      <c r="K338" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -37606,7 +37624,7 @@
           <t>30703152300692</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -37655,7 +37673,7 @@
           <t>30607012308627</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -37704,7 +37722,7 @@
           <t>30611262301781</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -37753,7 +37771,7 @@
           <t>30506082300932</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -37802,7 +37820,7 @@
           <t>30707272300403</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J6" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -37851,7 +37869,7 @@
           <t>30511132300754</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -37900,7 +37918,7 @@
           <t>30405132300687</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J8" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -37949,7 +37967,7 @@
           <t>30507102300981</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J9" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -37998,7 +38016,7 @@
           <t>30701012311586</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J10" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -38047,7 +38065,7 @@
           <t>30609102302973</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J11" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -38096,7 +38114,7 @@
           <t>30710012306441</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J12" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -38145,7 +38163,7 @@
           <t>30405172300175</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J13" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -38194,7 +38212,7 @@
           <t>31010162300303</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J14" s="0" t="inlineStr">
         <is>
           <t>2XL</t>
         </is>
@@ -38243,7 +38261,7 @@
           <t>30505092300403</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J15" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
@@ -38292,7 +38310,7 @@
           <t>30512302300033</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J16" s="0" t="inlineStr">
         <is>
           <t>L</t>
         </is>
@@ -38341,7 +38359,7 @@
           <t>30703072302325</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J17" s="0" t="inlineStr">
         <is>
           <t>M</t>
         </is>
@@ -38390,7 +38408,7 @@
           <t>30601242102175</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J18" s="0" t="inlineStr">
         <is>
           <t>3XL</t>
         </is>
@@ -38439,7 +38457,7 @@
           <t>30705012407074</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J19" s="0" t="inlineStr">
         <is>
           <t>XL</t>
         </is>
